--- a/task1/Sample - Superstore.xlsx
+++ b/task1/Sample - Superstore.xlsx
@@ -5,10 +5,10 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data analysis\VA\task1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data analysis\VOLTIX\task1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCB776BF-08A7-4D0A-A653-9F28DB55B202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF7579B-32BE-46BA-AD61-5B9146B97E4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{92D5F8EE-0999-4248-97B1-3CD8E7CC6799}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <pivotCache cacheId="0" r:id="rId4"/>
     <pivotCache cacheId="1" r:id="rId5"/>
     <pivotCache cacheId="2" r:id="rId6"/>
-    <pivotCache cacheId="3" r:id="rId7"/>
+    <pivotCache cacheId="6" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -336,7 +336,16 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;[Red]&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;[Red]&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;[Red]&quot;$&quot;#,##0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;[Red]&quot;$&quot;#,##0"/>
     </dxf>
@@ -345,12 +354,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;[Red]&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;[Red]&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;[Red]&quot;$&quot;#,##0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -379,7 +382,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Saleh_Hatem_Elsoudy.xlsx]Pivots!PivotTable1</c:name>
+    <c:name>[Sample - Superstore.xlsx]Pivots!PivotTable1</c:name>
     <c:fmtId val="7"/>
   </c:pivotSource>
   <c:chart>
@@ -1761,7 +1764,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Saleh_Hatem_Elsoudy.xlsx]Pivots!PivotTable3</c:name>
+    <c:name>[Sample - Superstore.xlsx]Pivots!PivotTable3</c:name>
     <c:fmtId val="11"/>
   </c:pivotSource>
   <c:chart>
@@ -2398,7 +2401,7 @@
           </c:txPr>
           <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="1"/>
@@ -2609,7 +2612,7 @@
             </c:txPr>
             <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
+            <c:showVal val="1"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="1"/>
@@ -2796,7 +2799,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Saleh_Hatem_Elsoudy.xlsx]Pivots!PivotTable2</c:name>
+    <c:name>[Sample - Superstore.xlsx]Pivots!PivotTable2</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
@@ -3410,7 +3413,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Saleh_Hatem_Elsoudy.xlsx]Pivots!PivotTable5</c:name>
+    <c:name>[Sample - Superstore.xlsx]Pivots!PivotTable5</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
@@ -3705,8 +3708,8 @@
           <c:idx val="0"/>
           <c:layout>
             <c:manualLayout>
-              <c:x val="-0.10246325459317586"/>
-              <c:y val="0.12962962962962962"/>
+              <c:x val="-1.9129921259842621E-2"/>
+              <c:y val="0.16203703703703695"/>
             </c:manualLayout>
           </c:layout>
           <c:spPr>
@@ -3881,8 +3884,8 @@
           <c:idx val="0"/>
           <c:layout>
             <c:manualLayout>
-              <c:x val="-0.15000000000000002"/>
-              <c:y val="9.2592592592592587E-2"/>
+              <c:x val="-6.6666666666666666E-2"/>
+              <c:y val="-0.12037037037037036"/>
             </c:manualLayout>
           </c:layout>
           <c:spPr>
@@ -4233,8 +4236,8 @@
           <c:idx val="0"/>
           <c:layout>
             <c:manualLayout>
-              <c:x val="-2.7777777777778798E-3"/>
-              <c:y val="-0.16203703703703712"/>
+              <c:x val="-5.5555555555555552E-2"/>
+              <c:y val="-7.407407407407407E-2"/>
             </c:manualLayout>
           </c:layout>
           <c:spPr>
@@ -4409,8 +4412,8 @@
           <c:idx val="0"/>
           <c:layout>
             <c:manualLayout>
-              <c:x val="1.1111111111111112E-2"/>
-              <c:y val="-8.3333333333333329E-2"/>
+              <c:x val="-4.7222222222222221E-2"/>
+              <c:y val="-0.12037037037037046"/>
             </c:manualLayout>
           </c:layout>
           <c:spPr>
@@ -4497,8 +4500,8 @@
           <c:idx val="0"/>
           <c:layout>
             <c:manualLayout>
-              <c:x val="1.6666666666666767E-2"/>
-              <c:y val="-5.5555555555555643E-2"/>
+              <c:x val="-2.5000000000000012E-2"/>
+              <c:y val="-0.1435185185185186"/>
             </c:manualLayout>
           </c:layout>
           <c:spPr>
@@ -4980,8 +4983,8 @@
               <c:idx val="0"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-5.833333333333323E-2"/>
-                  <c:y val="-7.4074074074074056E-2"/>
+                  <c:x val="-2.5000000000000012E-2"/>
+                  <c:y val="-0.1435185185185186"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -5001,8 +5004,8 @@
               <c:idx val="1"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-0.10246325459317586"/>
-                  <c:y val="0.12962962962962962"/>
+                  <c:x val="4.9999999999999899E-2"/>
+                  <c:y val="-4.6296296296296294E-3"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -5022,8 +5025,8 @@
               <c:idx val="2"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-4.4444444444444446E-2"/>
-                  <c:y val="-8.7962962962962965E-2"/>
+                  <c:x val="-6.6666666666666666E-2"/>
+                  <c:y val="-0.12037037037037036"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -5043,8 +5046,8 @@
               <c:idx val="3"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-0.15000000000000002"/>
-                  <c:y val="9.2592592592592587E-2"/>
+                  <c:x val="-4.7222222222222221E-2"/>
+                  <c:y val="-0.12037037037037046"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -5064,8 +5067,8 @@
               <c:idx val="4"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-6.1111111111111109E-2"/>
-                  <c:y val="0.20833333333333334"/>
+                  <c:x val="0"/>
+                  <c:y val="-0.15277777777777779"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -5085,8 +5088,8 @@
               <c:idx val="5"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-1.9444444444444445E-2"/>
-                  <c:y val="0.1203703703703702"/>
+                  <c:x val="-1.6666666666666666E-2"/>
+                  <c:y val="0.10648148148148148"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -5106,8 +5109,8 @@
               <c:idx val="6"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="0"/>
-                  <c:y val="-0.15277777777777779"/>
+                  <c:x val="-5.5555555555555552E-2"/>
+                  <c:y val="-7.407407407407407E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -5127,8 +5130,8 @@
               <c:idx val="7"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-1.6666666666666666E-2"/>
-                  <c:y val="0.10648148148148148"/>
+                  <c:x val="-1.9444444444444445E-2"/>
+                  <c:y val="0.1203703703703702"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -5148,8 +5151,8 @@
               <c:idx val="8"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-2.7777777777778798E-3"/>
-                  <c:y val="-0.16203703703703712"/>
+                  <c:x val="-4.4444444444444446E-2"/>
+                  <c:y val="-8.7962962962962965E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -5169,8 +5172,8 @@
               <c:idx val="9"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="1.1111111111111112E-2"/>
-                  <c:y val="-8.3333333333333329E-2"/>
+                  <c:x val="-6.1111111111111109E-2"/>
+                  <c:y val="0.20833333333333334"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -5190,8 +5193,8 @@
               <c:idx val="10"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="1.6666666666666767E-2"/>
-                  <c:y val="-5.5555555555555643E-2"/>
+                  <c:x val="-5.833333333333323E-2"/>
+                  <c:y val="-7.4074074074074056E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -5211,8 +5214,8 @@
               <c:idx val="11"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="4.9999999999999899E-2"/>
-                  <c:y val="-4.6296296296296294E-3"/>
+                  <c:x val="-1.9129921259842621E-2"/>
+                  <c:y val="0.16203703703703695"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -5289,40 +5292,40 @@
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mar</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Apr</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jun</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jul</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Aug</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Sep</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Oct</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>Nov</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="11">
                   <c:v>Dec</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Sep</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Mar</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Oct</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Aug</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>May</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Jun</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Jul</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Apr</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Jan</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Feb</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5334,40 +5337,40 @@
                 <c:formatCode>"$"#,##0;[Red]"$"#,##0</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
+                  <c:v>94924.835600000006</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>59751.251400000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>205005.48879999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>137762.1286</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>155028.81169999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>152718.67929999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>147238.09700000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>159044.06299999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>307649.94569999998</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>200322.9847</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>352461.071</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="11">
                   <c:v>325293.50349999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>307649.94569999998</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>205005.48879999999</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>200322.9847</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>159044.06299999999</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>155028.81169999999</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>152718.67929999999</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>147238.09700000001</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>137762.1286</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>94924.835600000006</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>59751.251400000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5477,34 +5480,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:extLst>
@@ -5552,7 +5527,6 @@
         <c14:dropZoneFilter val="1"/>
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
       </c14:pivotOptions>
     </c:ext>
     <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
@@ -8212,7 +8186,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Saleh Hatem" refreshedDate="46272.747703356479" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{411BD577-216B-4EFC-8DF2-0F4194886B45}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Saleh Hatem" refreshedDate="46313.751682754628" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{411BD577-216B-4EFC-8DF2-0F4194886B45}">
   <cacheSource type="external" connectionId="2"/>
   <cacheFields count="3">
     <cacheField name="[Measures].[Sum of Sales]" caption="Sum of Sales" numFmtId="0" hierarchy="27" level="32767"/>
@@ -8317,395 +8291,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E768D885-E21C-46EA-AAD6-337C72CE3ADD}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="F1:G12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="3">
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField allDrilled="1" subtotalTop="0" showAll="0" sortType="descending" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="17">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" measureFilter="1" sortType="ascending" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="10">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="11">
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Total Sales" fld="0" baseField="0" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="0">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="1">
-    <chartFormat chart="3" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotHierarchies count="29">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToData="1" caption="Total Sales"/>
-    <pivotHierarchy dragToData="1"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="2" type="count" id="1" iMeasureHier="27">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="10" filterVal="10"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
-  <rowHierarchiesUsage count="1">
-    <rowHierarchyUsage hierarchyUsage="16"/>
-  </rowHierarchiesUsage>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings>
-        <x15:activeTabTopLevelEntity name="[Sample - Superstore]"/>
-      </x15:pivotTableUISettings>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{312FDA41-1F48-4E4F-B0A3-A164A250B058}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
-  <location ref="A1:C5" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="3">
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Total Sales" fld="0" baseField="2" baseItem="0" numFmtId="164"/>
-    <dataField name="Total Profit" fld="1" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="2">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="1">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="8">
-    <chartFormat chart="7" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="9" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="10">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="11">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="12">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="13">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="14">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="15">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotHierarchies count="29">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToData="1" caption="Total Sales"/>
-    <pivotHierarchy dragToData="1" caption="Total Profit"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <rowHierarchiesUsage count="1">
-    <rowHierarchyUsage hierarchyUsage="14"/>
-  </rowHierarchiesUsage>
-  <colHierarchiesUsage count="1">
-    <colHierarchyUsage hierarchyUsage="-2"/>
-  </colHierarchiesUsage>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings>
-        <x15:activeTabTopLevelEntity name="[Sample - Superstore]"/>
-      </x15:pivotTableUISettings>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{970EF2EA-09BF-48B4-BBA4-0C03949088AA}" name="PivotTable5" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{970EF2EA-09BF-48B4-BBA4-0C03949088AA}" name="PivotTable5" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
   <location ref="D17:E30" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
@@ -8726,7 +8312,7 @@
         </pivotArea>
       </autoSortScope>
     </pivotField>
-    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" sortType="descending" defaultSubtotal="0" defaultAttributeDrillState="1">
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" sortType="ascending" defaultSubtotal="0" defaultAttributeDrillState="1">
       <items count="12">
         <item x="0"/>
         <item x="1"/>
@@ -8741,15 +8327,6 @@
         <item x="10"/>
         <item x="11"/>
       </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
     </pivotField>
   </pivotFields>
   <rowFields count="1">
@@ -8757,22 +8334,16 @@
   </rowFields>
   <rowItems count="13">
     <i>
-      <x v="10"/>
+      <x/>
     </i>
     <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="8"/>
+      <x v="1"/>
     </i>
     <i>
       <x v="2"/>
     </i>
     <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="7"/>
+      <x v="3"/>
     </i>
     <i>
       <x v="4"/>
@@ -8784,13 +8355,19 @@
       <x v="6"/>
     </i>
     <i>
-      <x v="3"/>
+      <x v="7"/>
     </i>
     <i>
-      <x/>
+      <x v="8"/>
     </i>
     <i>
-      <x v="1"/>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
     </i>
     <i t="grand">
       <x/>
@@ -8803,7 +8380,7 @@
     <dataField name="Total Sales" fld="0" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="3">
+    <format dxfId="1">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -9013,7 +8590,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{605B6A41-2072-478F-9F65-D4F64DACC7E8}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
   <location ref="A9:B14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
@@ -9063,7 +8640,7 @@
     <dataField name="Total Sales" fld="0" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="4">
+    <format dxfId="2">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -9161,6 +8738,394 @@
   <rowHierarchiesUsage count="1">
     <rowHierarchyUsage hierarchyUsage="12"/>
   </rowHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings>
+        <x15:activeTabTopLevelEntity name="[Sample - Superstore]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E768D885-E21C-46EA-AAD6-337C72CE3ADD}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="F1:G12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField allDrilled="1" subtotalTop="0" showAll="0" sortType="descending" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="17">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" measureFilter="1" sortType="ascending" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="10">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="11">
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Total Sales" fld="0" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="3">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="1">
+    <chartFormat chart="3" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotHierarchies count="29">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1" caption="Total Sales"/>
+    <pivotHierarchy dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="2" type="count" id="1" iMeasureHier="27">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="10" filterVal="10"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="16"/>
+  </rowHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings>
+        <x15:activeTabTopLevelEntity name="[Sample - Superstore]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{312FDA41-1F48-4E4F-B0A3-A164A250B058}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
+  <location ref="A1:C5" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Total Sales" fld="0" baseField="2" baseItem="0" numFmtId="164"/>
+    <dataField name="Total Profit" fld="1" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="5">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="4">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="8">
+    <chartFormat chart="7" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="10">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="11">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="12">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="13">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="14">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="15">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotHierarchies count="29">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1" caption="Total Sales"/>
+    <pivotHierarchy dragToData="1" caption="Total Profit"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="14"/>
+  </rowHierarchiesUsage>
+  <colHierarchiesUsage count="1">
+    <colHierarchyUsage hierarchyUsage="-2"/>
+  </colHierarchiesUsage>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
@@ -9797,98 +9762,98 @@
     </row>
     <row r="18" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D18" s="2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E18" s="3">
-        <v>352461.071</v>
+        <v>94924.835600000006</v>
       </c>
     </row>
     <row r="19" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D19" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E19" s="3">
-        <v>325293.50349999999</v>
+        <v>59751.251400000001</v>
       </c>
     </row>
     <row r="20" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D20" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E20" s="3">
-        <v>307649.94569999998</v>
+        <v>205005.48879999999</v>
       </c>
     </row>
     <row r="21" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E21" s="3">
-        <v>205005.48879999999</v>
+        <v>137762.1286</v>
       </c>
     </row>
     <row r="22" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D22" s="2" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E22" s="3">
-        <v>200322.9847</v>
+        <v>155028.81169999999</v>
       </c>
     </row>
     <row r="23" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D23" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E23" s="3">
-        <v>159044.06299999999</v>
+        <v>152718.67929999999</v>
       </c>
     </row>
     <row r="24" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D24" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E24" s="3">
-        <v>155028.81169999999</v>
+        <v>147238.09700000001</v>
       </c>
     </row>
     <row r="25" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D25" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E25" s="3">
-        <v>152718.67929999999</v>
+        <v>159044.06299999999</v>
       </c>
     </row>
     <row r="26" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D26" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E26" s="3">
-        <v>147238.09700000001</v>
+        <v>307649.94569999998</v>
       </c>
     </row>
     <row r="27" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D27" s="2" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E27" s="3">
-        <v>137762.1286</v>
+        <v>200322.9847</v>
       </c>
     </row>
     <row r="28" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D28" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E28" s="3">
-        <v>94924.835600000006</v>
+        <v>352461.071</v>
       </c>
     </row>
     <row r="29" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D29" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E29" s="3">
-        <v>59751.251400000001</v>
+        <v>325293.50349999999</v>
       </c>
     </row>
     <row r="30" spans="4:5" x14ac:dyDescent="0.3">
